--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -63,29 +63,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>BRAKE</t>
   </si>
   <si>
-    <t>brake</t>
+    <t>Brake</t>
   </si>
   <si>
     <t>ENGINE</t>
   </si>
   <si>
-    <t>engine</t>
+    <t>Engine</t>
   </si>
   <si>
     <t>Failed</t>
   </si>
   <si>
-    <t/>
+    <t>Game Failed</t>
   </si>
   <si>
     <t>GameOverUIForm.Back</t>
   </si>
   <si>
+    <t>Back</t>
+  </si>
+  <si>
     <t>Level.DisplayName1</t>
   </si>
   <si>
@@ -119,21 +122,27 @@
     <t>MenuUIForm.Tips</t>
   </si>
   <si>
-    <t>Click to start</t>
+    <t>Tap to Start</t>
   </si>
   <si>
     <t>Nothing</t>
   </si>
   <si>
-    <t>Not implemented</t>
+    <t>Not Implemented</t>
   </si>
   <si>
     <t>OFF</t>
   </si>
   <si>
+    <t>Off</t>
+  </si>
+  <si>
     <t>ON</t>
   </si>
   <si>
+    <t>On</t>
+  </si>
+  <si>
     <t>RatingDialog.CancelTxt</t>
   </si>
   <si>
@@ -143,19 +152,19 @@
     <t>RatingDialog.Description</t>
   </si>
   <si>
-    <t>Have you enjoyed the our game?\n&lt;size=130%&gt;Leave 5 star ratings in the App Store!</t>
+    <t>Do you like this game?\nPlease give us a 5-star rating!</t>
   </si>
   <si>
     <t>RatingDialog.HighRatingTips</t>
   </si>
   <si>
-    <t>Thank you for your affirmation! We will continue to work hard!</t>
+    <t>Thank you for your support! We will keep up the good work!</t>
   </si>
   <si>
     <t>RatingDialog.LowRatingTips</t>
   </si>
   <si>
-    <t>Thank you for your evaluation. We will do our best to improve and optimize it!</t>
+    <t>Thank you for your feedback, we will do our best to improve!</t>
   </si>
   <si>
     <t>RatingDialog.RateTxt</t>
@@ -164,6 +173,18 @@
     <t>Rate</t>
   </si>
   <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>Shop</t>
+  </si>
+  <si>
+    <t>STEERING</t>
+  </si>
+  <si>
+    <t>Steering</t>
+  </si>
+  <si>
     <t>Settings.Help</t>
   </si>
   <si>
@@ -179,28 +200,31 @@
     <t>Settings.Music</t>
   </si>
   <si>
-    <t>BGM</t>
+    <t>Music</t>
   </si>
   <si>
     <t>Settings.Privacy</t>
   </si>
   <si>
-    <t>Privacy</t>
+    <t>Privacy Policy</t>
   </si>
   <si>
     <t>Settings.Rating</t>
   </si>
   <si>
+    <t>Rating</t>
+  </si>
+  <si>
     <t>Settings.SFX</t>
   </si>
   <si>
-    <t>SFX</t>
+    <t>Sound Effects</t>
   </si>
   <si>
     <t>Settings.Title</t>
   </si>
   <si>
-    <t>SETTINGS</t>
+    <t>Settings</t>
   </si>
   <si>
     <t>Settings.Vibrate</t>
@@ -209,22 +233,10 @@
     <t>Vibration</t>
   </si>
   <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>Shop</t>
-  </si>
-  <si>
-    <t>STEERING</t>
-  </si>
-  <si>
-    <t>drive</t>
-  </si>
-  <si>
     <t>TermsOfService</t>
   </si>
   <si>
-    <t>Service Terms</t>
+    <t>Terms of Service</t>
   </si>
   <si>
     <t>UNLOCK</t>
@@ -415,6 +427,130 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -4022,250 +4158,250 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4280,7 +4416,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId150" name="A1">
+            <control shapeId="1056" r:id="rId180" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4302,7 +4438,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId151" name="A2">
+            <control shapeId="1057" r:id="rId181" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4324,7 +4460,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId152" name="A3">
+            <control shapeId="1058" r:id="rId182" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4346,7 +4482,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId153" name="A4">
+            <control shapeId="1059" r:id="rId183" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4368,7 +4504,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId154" name="A5">
+            <control shapeId="1060" r:id="rId184" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4390,7 +4526,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId155" name="A6">
+            <control shapeId="1061" r:id="rId185" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4412,7 +4548,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId156" name="A7">
+            <control shapeId="1062" r:id="rId186" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4434,7 +4570,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId157" name="A8">
+            <control shapeId="1063" r:id="rId187" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4456,7 +4592,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId158" name="A9">
+            <control shapeId="1064" r:id="rId188" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4478,7 +4614,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId159" name="A10">
+            <control shapeId="1065" r:id="rId189" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4500,7 +4636,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId160" name="A11">
+            <control shapeId="1066" r:id="rId190" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4522,7 +4658,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId161" name="A12">
+            <control shapeId="1067" r:id="rId191" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4544,7 +4680,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId162" name="A13">
+            <control shapeId="1068" r:id="rId192" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4566,7 +4702,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId163" name="A14">
+            <control shapeId="1069" r:id="rId193" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4588,7 +4724,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId164" name="A15">
+            <control shapeId="1070" r:id="rId194" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4610,7 +4746,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId165" name="A16">
+            <control shapeId="1071" r:id="rId195" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4632,7 +4768,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId166" name="A17">
+            <control shapeId="1072" r:id="rId196" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4654,7 +4790,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId167" name="A18">
+            <control shapeId="1073" r:id="rId197" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4676,7 +4812,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId168" name="A19">
+            <control shapeId="1074" r:id="rId198" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4698,7 +4834,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId169" name="A20">
+            <control shapeId="1075" r:id="rId199" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4720,7 +4856,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId170" name="A21">
+            <control shapeId="1076" r:id="rId200" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4742,7 +4878,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId171" name="A22">
+            <control shapeId="1077" r:id="rId201" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4764,7 +4900,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId172" name="A23">
+            <control shapeId="1078" r:id="rId202" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4786,7 +4922,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId173" name="A24">
+            <control shapeId="1079" r:id="rId203" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4808,7 +4944,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId174" name="A25">
+            <control shapeId="1080" r:id="rId204" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4830,7 +4966,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId175" name="A26">
+            <control shapeId="1081" r:id="rId205" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4852,7 +4988,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId176" name="A27">
+            <control shapeId="1082" r:id="rId206" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4874,7 +5010,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId177" name="A28">
+            <control shapeId="1083" r:id="rId207" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4896,7 +5032,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId178" name="A29">
+            <control shapeId="1084" r:id="rId208" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4918,7 +5054,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId179" name="A30">
+            <control shapeId="1085" r:id="rId209" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4940,7 +5076,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId180" name="A31">
+            <control shapeId="1086" r:id="rId210" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
